--- a/example/example/example_hansard.xlsx
+++ b/example/example/example_hansard.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28800" yWindow="600" windowWidth="38400" windowHeight="21000" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Participants" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,30 +13,23 @@
     <sheet name="Schedule" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -49,27 +43,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -82,20 +61,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -462,156 +437,156 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Assistant</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Assistant email</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Stacy Arnold</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Seth Lang</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>StacyArnold@email.com</t>
+          <t>SethLang@email.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Stacy Arnold</t>
+          <t>Seth Lang</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>StacyArnold@email.com</t>
+          <t>SethLang@email.com</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Alexandra Flynn</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Charles Brown</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AlexandraFlynn@email.com</t>
+          <t>CharlesBrown@email.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alexandra Flynn</t>
+          <t>Charles Brown</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AlexandraFlynn@email.com</t>
+          <t>CharlesBrown@email.com</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tracy Tran</t>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Mark Wilkins</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TracyTran@email.com</t>
+          <t>MarkWilkins@email.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tracy Tran</t>
+          <t>Mark Wilkins</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TracyTran@email.com</t>
+          <t>MarkWilkins@email.com</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Kathleen Salas</t>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Susan Solis</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KathleenSalas@email.com</t>
+          <t>SusanSolis@email.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kathleen Salas</t>
+          <t>Susan Solis</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KathleenSalas@email.com</t>
+          <t>SusanSolis@email.com</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Tyler Lewis</t>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Sophia Scott</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TylerLewis@email.com</t>
+          <t>SophiaScott@email.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tyler Lewis</t>
+          <t>Sophia Scott</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TylerLewis@email.com</t>
+          <t>SophiaScott@email.com</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Tanya Thomas</t>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Karen Miller</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TanyaThomas@email.com</t>
+          <t>KarenMiller@email.com</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tanya Thomas</t>
+          <t>Karen Miller</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TanyaThomas@email.com</t>
+          <t>KarenMiller@email.com</t>
         </is>
       </c>
     </row>
@@ -626,79 +601,85 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>End Date</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="n">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="n">
         <v>46082</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="3" t="n">
         <v>46096</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="3" t="n">
         <v>46096</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="3" t="n">
         <v>46110</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="3" t="n">
         <v>46110</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="3" t="n">
         <v>46124</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="3" t="n">
         <v>46124</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="3" t="n">
         <v>46138</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="3" t="n">
         <v>46138</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="3" t="n">
         <v>46152</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>46152</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>46166</v>
       </c>
     </row>
   </sheetData>
@@ -712,45 +693,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Period 1</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Period 2</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Period 3</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Period 4</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Period 5</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Period 6</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Stacy Arnold</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Seth Lang</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -768,11 +754,14 @@
       <c r="F2" t="n">
         <v>1</v>
       </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Alexandra Flynn</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Charles Brown</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -790,18 +779,21 @@
       <c r="F3" t="n">
         <v>1</v>
       </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tracy Tran</t>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Mark Wilkins</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -812,11 +804,14 @@
       <c r="F4" t="n">
         <v>1</v>
       </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Kathleen Salas</t>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Susan Solis</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -834,11 +829,14 @@
       <c r="F5" t="n">
         <v>1</v>
       </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Tyler Lewis</t>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Sophia Scott</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -856,11 +854,14 @@
       <c r="F6" t="n">
         <v>1</v>
       </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Tanya Thomas</t>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Karen Miller</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -876,6 +877,9 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -890,152 +894,265 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Person</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Period 1</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Period 2</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Period 3</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Period 4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Period 5</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Period 6</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Stacy Arnold</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Seth Lang</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kathleen Salas</t>
+          <t>Charles Brown</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Alexandra Flynn</t>
+          <t>Sophia Scott</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tracy Tran</t>
+          <t>Mark Wilkins</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Susan Solis</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Karen Miller</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Charles Brown</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Alexandra Flynn</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Charles Brown</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tyler Lewis</t>
+          <t>Seth Lang</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Stacy Arnold</t>
+          <t>Susan Solis</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tanya Thomas</t>
+          <t>Karen Miller</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Mark Wilkins</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sophia Scott</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Seth Lang</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tracy Tran</t>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Mark Wilkins</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tanya Thomas</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>Sophia Scott</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Karen Miller</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stacy Arnold</t>
+          <t>Seth Lang</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Charles Brown</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Susan Solis</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sophia Scott</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Kathleen Salas</t>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Susan Solis</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Stacy Arnold</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>Karen Miller</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Charles Brown</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tyler Lewis</t>
+          <t>Sophia Scott</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Seth Lang</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mark Wilkins</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Karen Miller</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Tyler Lewis</t>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Sophia Scott</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alexandra Flynn</t>
+          <t>Mark Wilkins</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tanya Thomas</t>
+          <t>Seth Lang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kathleen Salas</t>
+          <t>Susan Solis</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Karen Miller</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Charles Brown</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Mark Wilkins</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Tanya Thomas</t>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Karen Miller</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tracy Tran</t>
+          <t>Susan Solis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tyler Lewis</t>
+          <t>Mark Wilkins</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Alexandra Flynn</t>
+          <t>Charles Brown</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sophia Scott</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Seth Lang</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Susan Solis</t>
         </is>
       </c>
     </row>

--- a/example/example/example_hansard.xlsx
+++ b/example/example/example_hansard.xlsx
@@ -461,132 +461,132 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Seth Lang</t>
+          <t>Lauren Williams</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SethLang@email.com</t>
+          <t>LaurenWilliams@email.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Seth Lang</t>
+          <t>Lauren Williams</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SethLang@email.com</t>
+          <t>LaurenWilliams@email.com</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Charles Brown</t>
+          <t>Wesley Gray</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CharlesBrown@email.com</t>
+          <t>WesleyGray@email.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charles Brown</t>
+          <t>Wesley Gray</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CharlesBrown@email.com</t>
+          <t>WesleyGray@email.com</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Mark Wilkins</t>
+          <t>Amber Lawson</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MarkWilkins@email.com</t>
+          <t>AmberLawson@email.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mark Wilkins</t>
+          <t>Amber Lawson</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MarkWilkins@email.com</t>
+          <t>AmberLawson@email.com</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Susan Solis</t>
+          <t>Gabriel Arnold</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SusanSolis@email.com</t>
+          <t>GabrielArnold@email.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Susan Solis</t>
+          <t>Gabriel Arnold</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SusanSolis@email.com</t>
+          <t>GabrielArnold@email.com</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Sophia Scott</t>
+          <t>Allison Harris</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SophiaScott@email.com</t>
+          <t>AllisonHarris@email.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sophia Scott</t>
+          <t>Allison Harris</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SophiaScott@email.com</t>
+          <t>AllisonHarris@email.com</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Karen Miller</t>
+          <t>Beverly Clark</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KarenMiller@email.com</t>
+          <t>BeverlyClark@email.com</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Karen Miller</t>
+          <t>Beverly Clark</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KarenMiller@email.com</t>
+          <t>BeverlyClark@email.com</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -621,10 +621,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46082</v>
+        <v>46089</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>46096</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="3">
@@ -632,10 +632,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>46096</v>
+        <v>46103</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>46110</v>
+        <v>46117</v>
       </c>
     </row>
     <row r="4">
@@ -643,10 +643,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>46110</v>
+        <v>46117</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>46124</v>
+        <v>46131</v>
       </c>
     </row>
     <row r="5">
@@ -654,10 +654,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46124</v>
+        <v>46131</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>46138</v>
+        <v>46145</v>
       </c>
     </row>
     <row r="6">
@@ -665,10 +665,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46138</v>
+        <v>46145</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>46152</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="7">
@@ -676,10 +676,54 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>46166</v>
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>46173</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>46187</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>46187</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>46215</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>46229</v>
       </c>
     </row>
   </sheetData>
@@ -693,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,11 +776,31 @@
           <t>Period 6</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Period 7</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Period 8</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Period 9</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Period 10</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Seth Lang</t>
+          <t>Lauren Williams</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -755,13 +819,25 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Charles Brown</t>
+          <t>Wesley Gray</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -780,13 +856,25 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Mark Wilkins</t>
+          <t>Amber Lawson</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -805,13 +893,25 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Susan Solis</t>
+          <t>Gabriel Arnold</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -830,13 +930,25 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Sophia Scott</t>
+          <t>Allison Harris</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -855,13 +967,25 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Karen Miller</t>
+          <t>Beverly Clark</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -880,6 +1004,18 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -894,7 +1030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -933,226 +1069,366 @@
           <t>Period 6</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Period 7</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Period 8</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Period 9</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Period 10</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Seth Lang</t>
+          <t>Lauren Williams</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Charles Brown</t>
+          <t>Wesley Gray</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sophia Scott</t>
+          <t>Allison Harris</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mark Wilkins</t>
+          <t>Amber Lawson</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Susan Solis</t>
+          <t>Gabriel Arnold</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Karen Miller</t>
+          <t>Beverly Clark</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Charles Brown</t>
+          <t>Allison Harris</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Wesley Gray</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Amber Lawson</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Gabriel Arnold</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Beverly Clark</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Charles Brown</t>
+          <t>Wesley Gray</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Seth Lang</t>
+          <t>Lauren Williams</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Susan Solis</t>
+          <t>Gabriel Arnold</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Karen Miller</t>
+          <t>Beverly Clark</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mark Wilkins</t>
+          <t>Amber Lawson</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sophia Scott</t>
+          <t>Allison Harris</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Seth Lang</t>
+          <t>Gabriel Arnold</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Lauren Williams</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Beverly Clark</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Amber Lawson</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Allison Harris</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Mark Wilkins</t>
+          <t>Amber Lawson</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sophia Scott</t>
+          <t>Allison Harris</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Karen Miller</t>
+          <t>Beverly Clark</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Seth Lang</t>
+          <t>Lauren Williams</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Charles Brown</t>
+          <t>Wesley Gray</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Susan Solis</t>
+          <t>Gabriel Arnold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sophia Scott</t>
+          <t>Beverly Clark</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Allison Harris</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Lauren Williams</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Wesley Gray</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Gabriel Arnold</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Susan Solis</t>
+          <t>Gabriel Arnold</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Karen Miller</t>
+          <t>Beverly Clark</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charles Brown</t>
+          <t>Wesley Gray</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sophia Scott</t>
+          <t>Allison Harris</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seth Lang</t>
+          <t>Lauren Williams</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mark Wilkins</t>
+          <t>Amber Lawson</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Karen Miller</t>
+          <t>Wesley Gray</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Beverly Clark</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Allison Harris</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Lauren Williams</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Amber Lawson</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Sophia Scott</t>
+          <t>Allison Harris</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mark Wilkins</t>
+          <t>Amber Lawson</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seth Lang</t>
+          <t>Lauren Williams</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Susan Solis</t>
+          <t>Gabriel Arnold</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Karen Miller</t>
+          <t>Beverly Clark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Charles Brown</t>
+          <t>Wesley Gray</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mark Wilkins</t>
+          <t>Lauren Williams</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Amber Lawson</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Gabriel Arnold</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Beverly Clark</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Wesley Gray</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Karen Miller</t>
+          <t>Beverly Clark</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Susan Solis</t>
+          <t>Gabriel Arnold</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mark Wilkins</t>
+          <t>Amber Lawson</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Charles Brown</t>
+          <t>Wesley Gray</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sophia Scott</t>
+          <t>Allison Harris</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Seth Lang</t>
+          <t>Lauren Williams</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Susan Solis</t>
+          <t>Amber Lawson</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Gabriel Arnold</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Wesley Gray</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Allison Harris</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Lauren Williams</t>
         </is>
       </c>
     </row>

--- a/example/example/example_hansard.xlsx
+++ b/example/example/example_hansard.xlsx
@@ -461,132 +461,132 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Lauren Williams</t>
+          <t>Richard Lewis</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LaurenWilliams@email.com</t>
+          <t>RichardLewis@email.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lauren Williams</t>
+          <t>Richard Lewis</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LaurenWilliams@email.com</t>
+          <t>RichardLewis@email.com</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Wesley Gray</t>
+          <t>Shane Acosta</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WesleyGray@email.com</t>
+          <t>ShaneAcosta@email.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wesley Gray</t>
+          <t>Shane Acosta</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>WesleyGray@email.com</t>
+          <t>ShaneAcosta@email.com</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Amber Lawson</t>
+          <t>Brenda Leblanc</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AmberLawson@email.com</t>
+          <t>BrendaLeblanc@email.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amber Lawson</t>
+          <t>Brenda Leblanc</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AmberLawson@email.com</t>
+          <t>BrendaLeblanc@email.com</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Gabriel Arnold</t>
+          <t>Mark Gonzales</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GabrielArnold@email.com</t>
+          <t>MarkGonzales@email.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Gabriel Arnold</t>
+          <t>Mark Gonzales</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GabrielArnold@email.com</t>
+          <t>MarkGonzales@email.com</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Allison Harris</t>
+          <t>Jennifer Key</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AllisonHarris@email.com</t>
+          <t>JenniferKey@email.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Allison Harris</t>
+          <t>Jennifer Key</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AllisonHarris@email.com</t>
+          <t>JenniferKey@email.com</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Beverly Clark</t>
+          <t>Kristin Rivas</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BeverlyClark@email.com</t>
+          <t>KristinRivas@email.com</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Beverly Clark</t>
+          <t>Kristin Rivas</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BeverlyClark@email.com</t>
+          <t>KristinRivas@email.com</t>
         </is>
       </c>
     </row>
@@ -601,10 +601,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Start Date</t>
@@ -669,61 +674,6 @@
       </c>
       <c r="C6" s="3" t="n">
         <v>46159</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>46159</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>46173</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>46173</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>46187</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>46187</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>46201</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>46201</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>46215</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>46215</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>46229</v>
       </c>
     </row>
   </sheetData>
@@ -737,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,36 +721,11 @@
           <t>Period 5</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Period 6</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Period 7</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Period 8</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Period 9</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Period 10</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Lauren Williams</t>
+          <t>Richard Lewis</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -816,28 +741,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Wesley Gray</t>
+          <t>Shane Acosta</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -853,28 +763,13 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Amber Lawson</t>
+          <t>Brenda Leblanc</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -890,28 +785,13 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Gabriel Arnold</t>
+          <t>Mark Gonzales</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -927,28 +807,13 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Allison Harris</t>
+          <t>Jennifer Key</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -964,28 +829,13 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Beverly Clark</t>
+          <t>Kristin Rivas</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1001,21 +851,6 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1030,7 +865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1064,373 +899,102 @@
           <t>Period 5</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Period 6</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Period 7</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Period 8</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Period 9</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Period 10</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Lauren Williams</t>
+          <t>Richard Lewis</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wesley Gray</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Allison Harris</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Amber Lawson</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Gabriel Arnold</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Beverly Clark</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Allison Harris</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Wesley Gray</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Amber Lawson</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Gabriel Arnold</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Beverly Clark</t>
-        </is>
-      </c>
+          <t>Mark Gonzales</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Wesley Gray</t>
+          <t>Shane Acosta</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lauren Williams</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Gabriel Arnold</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Beverly Clark</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Amber Lawson</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Allison Harris</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Gabriel Arnold</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Lauren Williams</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Beverly Clark</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Amber Lawson</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Allison Harris</t>
-        </is>
-      </c>
+          <t>Jennifer Key</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Amber Lawson</t>
+          <t>Brenda Leblanc</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Allison Harris</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Beverly Clark</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Lauren Williams</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Wesley Gray</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Gabriel Arnold</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Beverly Clark</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Allison Harris</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Lauren Williams</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Wesley Gray</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Gabriel Arnold</t>
-        </is>
-      </c>
+          <t>Kristin Rivas</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Gabriel Arnold</t>
+          <t>Mark Gonzales</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Beverly Clark</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Wesley Gray</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Allison Harris</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Lauren Williams</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Amber Lawson</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Wesley Gray</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Beverly Clark</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Allison Harris</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Lauren Williams</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Amber Lawson</t>
-        </is>
-      </c>
+          <t>Richard Lewis</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Allison Harris</t>
+          <t>Jennifer Key</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amber Lawson</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Lauren Williams</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Gabriel Arnold</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Beverly Clark</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Wesley Gray</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Lauren Williams</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Amber Lawson</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Gabriel Arnold</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Beverly Clark</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Wesley Gray</t>
-        </is>
-      </c>
+          <t>Shane Acosta</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Beverly Clark</t>
+          <t>Kristin Rivas</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gabriel Arnold</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Amber Lawson</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Wesley Gray</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Allison Harris</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Lauren Williams</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Amber Lawson</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Gabriel Arnold</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Wesley Gray</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Allison Harris</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Lauren Williams</t>
-        </is>
-      </c>
+          <t>Brenda Leblanc</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
